--- a/Budget/data/budget_2023.xlsx
+++ b/Budget/data/budget_2023.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\NLP\anambra\Budget\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C050DF96-216E-4D24-B16D-D6E0824C2964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC5E8693-5F15-424F-96FB-1CF7D883F8E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4C321D3A-42E5-4E0E-A44F-0D891752FD89}"/>
   </bookViews>

--- a/Budget/data/budget_2023.xlsx
+++ b/Budget/data/budget_2023.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\NLP\anambra\Budget\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC5E8693-5F15-424F-96FB-1CF7D883F8E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{104A88F8-4A67-48BF-BB50-8E376FFBB9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4C321D3A-42E5-4E0E-A44F-0D891752FD89}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>Ministry</t>
   </si>
@@ -87,24 +87,12 @@
     <t>Judicial Service Commission</t>
   </si>
   <si>
-    <t>Anambra State Internal Revenue Service</t>
-  </si>
-  <si>
     <t>Ministry of Information</t>
   </si>
   <si>
     <t>Office of the Head of Service</t>
   </si>
   <si>
-    <t>Anambra State Investment Promotion &amp; Protection Agency</t>
-  </si>
-  <si>
-    <t>Christian Pilgrims Welfare Board</t>
-  </si>
-  <si>
-    <t>Muslim Pilgrims Welfare Board</t>
-  </si>
-  <si>
     <t>Ministry of Homeland Affairs</t>
   </si>
   <si>
@@ -136,12 +124,30 @@
   </si>
   <si>
     <t>Ministry of Lands</t>
+  </si>
+  <si>
+    <t>₦ ₦ 4,471,795,117.74</t>
+  </si>
+  <si>
+    <t>Office of the Auditor General (State)</t>
+  </si>
+  <si>
+    <t>Civil Service Commission</t>
+  </si>
+  <si>
+    <t>Local Government Civil Service Commission</t>
+  </si>
+  <si>
+    <t>Awka Capital Teritory Development Authority - ACTDA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="8" formatCode="&quot;₦&quot;#,##0.00;[Red]\-&quot;₦&quot;#,##0.00"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -151,9 +157,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -197,8 +203,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="8" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -519,8 +525,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBA8366D-6ECB-4F68-8AF6-727A75A0BB68}">
   <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="6" width="34.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -536,628 +545,628 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3">
-        <v>659829526.5</v>
-      </c>
-      <c r="C2" s="3">
-        <v>29607825825</v>
-      </c>
-      <c r="D2" s="3">
-        <v>36643366813</v>
-      </c>
-      <c r="E2" s="3">
-        <v>9200000000</v>
-      </c>
-      <c r="F2" s="3">
-        <v>45843366813</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="2">
+        <v>4401856028.5699997</v>
+      </c>
+      <c r="C2" s="2">
+        <v>17713149739.400002</v>
+      </c>
+      <c r="D2" s="2">
+        <v>22115005767.970001</v>
+      </c>
+      <c r="E2" s="2">
+        <v>3268487325.8000002</v>
+      </c>
+      <c r="F2" s="2">
+        <v>25383493093.759998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3">
-        <v>479472582.30000001</v>
-      </c>
-      <c r="C3" s="3">
-        <v>641054701</v>
-      </c>
-      <c r="D3" s="3">
-        <v>1062501318</v>
-      </c>
-      <c r="E3" s="3">
-        <v>2646000000</v>
-      </c>
-      <c r="F3" s="3">
-        <v>3708501318</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="2">
+        <v>350074643.94999999</v>
+      </c>
+      <c r="C3" s="2">
+        <v>685823357.25</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1035898001.2</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1712205500</v>
+      </c>
+      <c r="F3" s="2">
+        <v>2748103501.1999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3">
-        <v>329861189.19999999</v>
-      </c>
-      <c r="C4" s="3">
-        <v>23812946.48</v>
-      </c>
-      <c r="D4" s="3">
-        <v>353674135.69999999</v>
-      </c>
-      <c r="E4" s="3">
-        <v>6125500000</v>
-      </c>
-      <c r="F4" s="3">
-        <v>6475174136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>15591770840.450001</v>
+      </c>
+      <c r="C4" s="2">
+        <v>31320111690.25</v>
+      </c>
+      <c r="D4" s="2">
+        <v>46911882530.699997</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3457500000</v>
+      </c>
+      <c r="F4" s="2">
+        <v>50369382530.699997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3">
-        <v>195899318.19999999</v>
-      </c>
-      <c r="C5" s="3">
-        <v>33427354.550000001</v>
-      </c>
-      <c r="D5" s="3">
-        <v>239326672.80000001</v>
-      </c>
-      <c r="E5" s="3">
-        <v>265320000000</v>
-      </c>
-      <c r="F5" s="3">
-        <v>268713266673</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
+        <v>170040879</v>
+      </c>
+      <c r="C5" s="2">
+        <v>13492500</v>
+      </c>
+      <c r="D5" s="2">
+        <v>183533379</v>
+      </c>
+      <c r="E5" s="2">
+        <v>80351500000</v>
+      </c>
+      <c r="F5" s="2">
+        <v>80535033379</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3">
-        <v>275336206.80000001</v>
-      </c>
-      <c r="C6" s="3">
-        <v>87971382.079999998</v>
-      </c>
-      <c r="D6" s="3">
-        <v>273088351.69999999</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3">
-        <v>273088351.69999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>94957181.560000002</v>
+      </c>
+      <c r="C6" s="2">
+        <v>197400000</v>
+      </c>
+      <c r="D6" s="2">
+        <v>292357181.56</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2752199954</v>
+      </c>
+      <c r="F6" s="2">
+        <v>3044557135.5599999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="3">
-        <v>593367392.20000005</v>
-      </c>
-      <c r="C7" s="3">
-        <v>19339716.079999998</v>
-      </c>
-      <c r="D7" s="3">
-        <v>621057108.29999995</v>
-      </c>
-      <c r="E7" s="3">
-        <v>3095000000</v>
-      </c>
-      <c r="F7" s="3">
-        <v>3708707108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="2">
+        <v>203730265</v>
+      </c>
+      <c r="C7" s="2">
+        <v>19792500</v>
+      </c>
+      <c r="D7" s="2">
+        <v>223522765</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1595000000</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1818522765</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="3">
-        <v>115066559.5</v>
-      </c>
-      <c r="C8" s="3">
-        <v>12384103.65</v>
-      </c>
-      <c r="D8" s="3">
-        <v>123450663.09999999</v>
-      </c>
-      <c r="E8" s="3">
-        <v>10211000000</v>
-      </c>
-      <c r="F8" s="3">
-        <v>10334450663</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2">
+        <v>73679058.25</v>
+      </c>
+      <c r="C8" s="2">
+        <v>6300000</v>
+      </c>
+      <c r="D8" s="2">
+        <v>79979058.25</v>
+      </c>
+      <c r="E8" s="2">
+        <v>7711000000</v>
+      </c>
+      <c r="F8" s="2">
+        <v>7790979058.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="3">
-        <v>105311864</v>
-      </c>
-      <c r="C9" s="3">
-        <v>13984967.33</v>
-      </c>
-      <c r="D9" s="3">
-        <v>117296831.3</v>
-      </c>
-      <c r="E9" s="3">
-        <v>389000000</v>
-      </c>
-      <c r="F9" s="3">
-        <v>506296831.30000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="2">
+        <v>18734364</v>
+      </c>
+      <c r="C9" s="2">
+        <v>6300000</v>
+      </c>
+      <c r="D9" s="2">
+        <v>25034364</v>
+      </c>
+      <c r="E9" s="2">
+        <v>395000000</v>
+      </c>
+      <c r="F9" s="2">
+        <v>420034364</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="3">
-        <v>687308192.60000002</v>
-      </c>
-      <c r="C10" s="3">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3">
-        <v>687308192.60000002</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3">
-        <v>687308192.60000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="2">
+        <v>27918612.030000001</v>
+      </c>
+      <c r="C10" s="2">
+        <v>6300000</v>
+      </c>
+      <c r="D10" s="2">
+        <v>34218612.030000001</v>
+      </c>
+      <c r="E10" s="2">
+        <v>3484000000</v>
+      </c>
+      <c r="F10" s="2">
+        <v>3518218612.0300002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="3">
-        <v>498275684.10000002</v>
-      </c>
-      <c r="C11" s="3">
-        <v>17705378.600000001</v>
-      </c>
-      <c r="D11" s="3">
-        <v>423892105.19999999</v>
-      </c>
-      <c r="E11" s="3">
-        <v>14046833333</v>
-      </c>
-      <c r="F11" s="3">
-        <v>18485743337</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="2">
+        <v>171394996.25</v>
+      </c>
+      <c r="C11" s="2">
+        <v>20473986.75</v>
+      </c>
+      <c r="D11" s="2">
+        <v>191868983</v>
+      </c>
+      <c r="E11" s="2">
+        <v>7123000000</v>
+      </c>
+      <c r="F11" s="2">
+        <v>7314868983</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="3">
-        <v>21572200</v>
-      </c>
-      <c r="C12" s="3">
-        <v>18227600</v>
-      </c>
-      <c r="D12" s="3">
-        <v>40799800</v>
-      </c>
-      <c r="E12" s="3">
-        <v>925000000</v>
-      </c>
-      <c r="F12" s="3">
-        <v>953799800</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="2">
+        <v>14700000</v>
+      </c>
+      <c r="C12" s="2">
+        <v>6300000</v>
+      </c>
+      <c r="D12" s="2">
+        <v>21000000</v>
+      </c>
+      <c r="E12" s="2">
+        <v>445000000</v>
+      </c>
+      <c r="F12" s="2">
+        <v>466000000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="3">
-        <v>1539128693</v>
-      </c>
-      <c r="C13" s="3">
-        <v>3145100261</v>
-      </c>
-      <c r="D13" s="3">
-        <v>4704228954</v>
-      </c>
-      <c r="E13" s="3">
-        <v>5958000000</v>
-      </c>
-      <c r="F13" s="3">
-        <v>10662228954</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="2">
+        <v>787432944</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2302205000</v>
+      </c>
+      <c r="D13" s="2">
+        <v>3089637944</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3384070000</v>
+      </c>
+      <c r="F13" s="2">
+        <v>6473707944</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="3">
-        <v>68113487.5</v>
-      </c>
-      <c r="C14" s="3">
-        <v>17910052.690000001</v>
-      </c>
-      <c r="D14" s="3">
-        <v>89023540.189999998</v>
-      </c>
-      <c r="E14" s="3">
-        <v>175000000</v>
-      </c>
-      <c r="F14" s="3">
-        <v>264523540.19999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="2">
+        <v>43548750</v>
+      </c>
+      <c r="C14" s="2">
+        <v>16454588.85</v>
+      </c>
+      <c r="D14" s="2">
+        <v>60003338.850000001</v>
+      </c>
+      <c r="E14" s="2">
+        <v>89120000</v>
+      </c>
+      <c r="F14" s="2">
+        <v>149123338.84999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="3">
-        <v>5783750263</v>
-      </c>
-      <c r="C15" s="3">
-        <v>81849237.680000007</v>
-      </c>
-      <c r="D15" s="3">
-        <v>5962263617</v>
-      </c>
-      <c r="E15" s="3">
-        <v>7885600000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>13857863617</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="2">
+        <v>1899355117.74</v>
+      </c>
+      <c r="C15" s="2">
+        <v>198660000</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2098015117.74</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2373780000</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="3">
-        <v>545015287.39999998</v>
-      </c>
-      <c r="C16" s="3">
-        <v>99712371.739999995</v>
-      </c>
-      <c r="D16" s="3">
-        <v>654727659.10000002</v>
-      </c>
-      <c r="E16" s="3">
-        <v>689000000</v>
-      </c>
-      <c r="F16" s="3">
-        <v>1343727659</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="2">
+        <v>195052501.69999999</v>
+      </c>
+      <c r="C16" s="2">
+        <v>667071311</v>
+      </c>
+      <c r="D16" s="2">
+        <v>862123812.70000005</v>
+      </c>
+      <c r="E16" s="2">
+        <v>647900000</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1510023812.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="3">
-        <v>283066530.19999999</v>
-      </c>
-      <c r="C17" s="3">
-        <v>18211374</v>
-      </c>
-      <c r="D17" s="3">
-        <v>302277904.19999999</v>
-      </c>
-      <c r="E17" s="3">
-        <v>5343118000</v>
-      </c>
-      <c r="F17" s="3">
-        <v>5625395904</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="2">
+        <v>521301065</v>
+      </c>
+      <c r="C17" s="2">
+        <v>65120000</v>
+      </c>
+      <c r="D17" s="2">
+        <v>586421065</v>
+      </c>
+      <c r="E17" s="2">
+        <v>530942000</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1117363065</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="3">
-        <v>1046410186</v>
-      </c>
-      <c r="C18" s="3">
-        <v>285920722.10000002</v>
-      </c>
-      <c r="D18" s="3">
-        <v>1332330908</v>
-      </c>
-      <c r="E18" s="3">
-        <v>856000000</v>
-      </c>
-      <c r="F18" s="3">
-        <v>2188330908</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="2">
+        <v>90701175</v>
+      </c>
+      <c r="C18" s="2">
+        <v>6300000</v>
+      </c>
+      <c r="D18" s="2">
+        <v>97001175</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1262180000</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1359181175</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="3">
-        <v>211583990</v>
-      </c>
-      <c r="C19" s="3">
-        <v>0</v>
-      </c>
-      <c r="D19" s="3">
-        <v>211583990</v>
-      </c>
-      <c r="E19" s="3">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3">
-        <v>211583990</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="2">
+        <v>76437273</v>
+      </c>
+      <c r="C19" s="2">
+        <v>13965000</v>
+      </c>
+      <c r="D19" s="2">
+        <v>90402273</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2583000000</v>
+      </c>
+      <c r="F19" s="2">
+        <v>2673402273</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="3">
-        <v>7076500</v>
-      </c>
-      <c r="C20" s="3">
-        <v>0</v>
-      </c>
-      <c r="D20" s="3">
-        <v>7076500</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>7076500</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="2">
+        <v>68825119.099999994</v>
+      </c>
+      <c r="C20" s="2">
+        <v>18900000</v>
+      </c>
+      <c r="D20" s="2">
+        <v>87725119.099999994</v>
+      </c>
+      <c r="E20" s="2">
+        <v>6945000000</v>
+      </c>
+      <c r="F20" s="2">
+        <v>7032725119.1000004</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="3">
-        <v>7010350</v>
-      </c>
-      <c r="C21" s="3">
-        <v>0</v>
-      </c>
-      <c r="D21" s="3">
-        <v>7010350</v>
-      </c>
-      <c r="E21" s="3">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3">
-        <v>7010350</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="2">
+        <v>141982924.59999999</v>
+      </c>
+      <c r="C21" s="2">
+        <v>19425000</v>
+      </c>
+      <c r="D21" s="2">
+        <v>161407924.59999999</v>
+      </c>
+      <c r="E21" s="2">
+        <v>562000000</v>
+      </c>
+      <c r="F21" s="2">
+        <v>723407924.60000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="3">
-        <v>133779993.09999999</v>
-      </c>
-      <c r="C22" s="3">
-        <v>14107400</v>
-      </c>
-      <c r="D22" s="3">
-        <v>145887393.09999999</v>
-      </c>
-      <c r="E22" s="3">
-        <v>2651500000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>2792387393</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="2">
+        <v>144784213.55000001</v>
+      </c>
+      <c r="C22" s="2">
+        <v>19171104.550000001</v>
+      </c>
+      <c r="D22" s="2">
+        <v>163955318.09999999</v>
+      </c>
+      <c r="E22" s="2">
+        <v>4000000000</v>
+      </c>
+      <c r="F22" s="2">
+        <v>4163955318.0999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="3">
-        <v>112446652.8</v>
-      </c>
-      <c r="C23" s="3">
-        <v>9551322</v>
-      </c>
-      <c r="D23" s="3">
-        <v>122197974.8</v>
-      </c>
-      <c r="E23" s="3">
-        <v>2590600000</v>
-      </c>
-      <c r="F23" s="3">
-        <v>2932226775</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="2">
+        <v>28547508.199999999</v>
+      </c>
+      <c r="C23" s="2">
+        <v>169575000</v>
+      </c>
+      <c r="D23" s="2">
+        <v>198122508.19999999</v>
+      </c>
+      <c r="E23" s="2">
+        <v>3120610000</v>
+      </c>
+      <c r="F23" s="2">
+        <v>3318732508.1999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="3">
-        <v>136600177.30000001</v>
-      </c>
-      <c r="C24" s="3">
-        <v>12860000</v>
-      </c>
-      <c r="D24" s="3">
-        <v>150460177.30000001</v>
-      </c>
-      <c r="E24" s="3">
-        <v>10175000000</v>
-      </c>
-      <c r="F24" s="3">
-        <v>10399650177</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="2">
+        <v>407252853.97000003</v>
+      </c>
+      <c r="C24" s="2">
+        <v>50699880</v>
+      </c>
+      <c r="D24" s="2">
+        <v>457952733.97000003</v>
+      </c>
+      <c r="E24" s="2">
+        <v>2065357129.3</v>
+      </c>
+      <c r="F24" s="2">
+        <v>2523309863.27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="3">
-        <v>275883462.60000002</v>
-      </c>
-      <c r="C25" s="3">
-        <v>20656250</v>
-      </c>
-      <c r="D25" s="3">
-        <v>297539712.60000002</v>
-      </c>
-      <c r="E25" s="3">
-        <v>537000000</v>
-      </c>
-      <c r="F25" s="3">
-        <v>834093412.60000002</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="2">
+        <v>7474159597.5699997</v>
+      </c>
+      <c r="C25" s="2">
+        <v>377711201.69999999</v>
+      </c>
+      <c r="D25" s="2">
+        <v>7851870799.2700005</v>
+      </c>
+      <c r="E25" s="2">
+        <v>6637912828.1800003</v>
+      </c>
+      <c r="F25" s="2">
+        <v>14489783627.450001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="3">
-        <v>188035997.80000001</v>
-      </c>
-      <c r="C26" s="3">
-        <v>59476821.460000001</v>
-      </c>
-      <c r="D26" s="3">
-        <v>249512819.30000001</v>
-      </c>
-      <c r="E26" s="3">
-        <v>3511000000</v>
-      </c>
-      <c r="F26" s="3">
-        <v>600612819.29999995</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="2">
+        <v>106646641.65000001</v>
+      </c>
+      <c r="C26" s="2">
+        <v>41292405</v>
+      </c>
+      <c r="D26" s="2">
+        <v>147939046.65000001</v>
+      </c>
+      <c r="E26" s="2">
+        <v>5496057500</v>
+      </c>
+      <c r="F26" s="2">
+        <v>5643996546.6499996</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="3">
-        <v>251024782.19999999</v>
-      </c>
-      <c r="C27" s="3">
-        <v>12860000</v>
-      </c>
-      <c r="D27" s="3">
-        <v>264884782.19999999</v>
-      </c>
-      <c r="E27" s="3">
-        <v>3379700000</v>
-      </c>
-      <c r="F27" s="3">
-        <v>3654814782</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="2">
+        <v>3252810278.4899998</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1658630341.1500001</v>
+      </c>
+      <c r="D27" s="2">
+        <v>4911440619.6400003</v>
+      </c>
+      <c r="E27" s="2">
+        <v>6203780519</v>
+      </c>
+      <c r="F27" s="2">
+        <v>11115221138.639999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="3">
-        <v>618826114.29999995</v>
-      </c>
-      <c r="C28" s="3">
-        <v>68476821.459999993</v>
-      </c>
-      <c r="D28" s="3">
-        <v>636970954.29999995</v>
-      </c>
-      <c r="E28" s="3">
-        <v>2776000000</v>
-      </c>
-      <c r="F28" s="3">
-        <v>914570954.29999995</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="2">
+        <v>194450647.15000001</v>
+      </c>
+      <c r="C28" s="2">
+        <v>236250000</v>
+      </c>
+      <c r="D28" s="2">
+        <v>430700647.14999998</v>
+      </c>
+      <c r="E28" s="2">
+        <v>430700647.14999998</v>
+      </c>
+      <c r="F28" s="2">
+        <v>2701918647.1500001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29" s="3">
-        <v>322935929.10000002</v>
-      </c>
-      <c r="C29" s="3">
-        <v>817764026.20000005</v>
-      </c>
-      <c r="D29" s="3">
-        <v>1150699955</v>
-      </c>
-      <c r="E29" s="3">
-        <v>37374500000</v>
-      </c>
-      <c r="F29" s="3">
-        <v>48881499955</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="B29" s="2">
+        <v>197267491.59999999</v>
+      </c>
+      <c r="C29" s="2">
+        <v>11025000</v>
+      </c>
+      <c r="D29" s="2">
+        <v>208292491.59999999</v>
+      </c>
+      <c r="E29" s="2">
+        <v>57200000</v>
+      </c>
+      <c r="F29" s="2">
+        <v>265492491.59999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="3">
-        <v>149732064.19999999</v>
-      </c>
-      <c r="C30" s="3">
-        <v>16822177.100000001</v>
-      </c>
-      <c r="D30" s="3">
-        <v>165554241.30000001</v>
-      </c>
-      <c r="E30" s="3">
-        <v>3304000000</v>
-      </c>
-      <c r="F30" s="3">
-        <v>490954241.30000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="B30" s="2">
+        <v>71243109.700000003</v>
+      </c>
+      <c r="C30" s="2">
+        <v>13650000</v>
+      </c>
+      <c r="D30" s="2">
+        <v>84893109.700000003</v>
+      </c>
+      <c r="E30" s="2">
+        <v>30000000</v>
+      </c>
+      <c r="F30" s="2">
+        <v>114893109.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" s="3">
-        <v>528449487.80000001</v>
-      </c>
-      <c r="C31" s="3">
+        <v>36</v>
+      </c>
+      <c r="B31" s="2">
+        <v>27627185.75</v>
+      </c>
+      <c r="C31" s="2">
         <v>0</v>
       </c>
-      <c r="D31" s="3">
-        <v>528449487.80000001</v>
-      </c>
-      <c r="E31" s="3">
+      <c r="D31" s="2">
+        <v>27627185.75</v>
+      </c>
+      <c r="E31" s="2">
         <v>0</v>
       </c>
-      <c r="F31" s="3">
-        <v>528449487.80000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F31" s="2">
+        <v>27627185.75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B32" s="3">
-        <v>268238168.19999999</v>
-      </c>
-      <c r="C32" s="3">
-        <v>19182554</v>
-      </c>
-      <c r="D32" s="3">
-        <v>288420722.19999999</v>
-      </c>
-      <c r="E32" s="3">
-        <v>1709000000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>459320722.19999999</v>
+        <v>37</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0</v>
+      </c>
+      <c r="C32" s="2">
+        <v>63210000</v>
+      </c>
+      <c r="D32" s="2">
+        <v>63210000</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2">
+        <v>63210000</v>
       </c>
     </row>
   </sheetData>
